--- a/fig/learn/so_freq.xlsx
+++ b/fig/learn/so_freq.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
   <si>
     <t>Word</t>
   </si>
@@ -37,153 +37,177 @@
     <t>omnisexual</t>
   </si>
   <si>
+    <t>im</t>
+  </si>
+  <si>
+    <t>questioning</t>
+  </si>
+  <si>
+    <t>and</t>
+  </si>
+  <si>
     <t>straight</t>
   </si>
   <si>
+    <t>but</t>
+  </si>
+  <si>
     <t>label</t>
   </si>
   <si>
-    <t>questioning</t>
+    <t>aromantic</t>
+  </si>
+  <si>
+    <t>the</t>
+  </si>
+  <si>
+    <t>non</t>
+  </si>
+  <si>
+    <t>to</t>
+  </si>
+  <si>
+    <t>not</t>
+  </si>
+  <si>
+    <t>pan</t>
+  </si>
+  <si>
+    <t>not sure</t>
+  </si>
+  <si>
+    <t>not straight</t>
+  </si>
+  <si>
+    <t>no label</t>
   </si>
   <si>
     <t>bisexual</t>
   </si>
   <si>
-    <t>aromantic</t>
-  </si>
-  <si>
     <t>panromantic</t>
   </si>
   <si>
-    <t>non</t>
-  </si>
-  <si>
     <t>biromantic</t>
   </si>
   <si>
-    <t>ace</t>
-  </si>
-  <si>
-    <t>sure</t>
+    <t>demiromantic</t>
+  </si>
+  <si>
+    <t>aro</t>
+  </si>
+  <si>
+    <t>spectrum</t>
+  </si>
+  <si>
+    <t>no</t>
   </si>
   <si>
     <t>unlabeled</t>
   </si>
   <si>
-    <t>pan</t>
+    <t>dont</t>
+  </si>
+  <si>
+    <t>labeled</t>
+  </si>
+  <si>
+    <t>bicurious</t>
   </si>
   <si>
     <t>know</t>
   </si>
   <si>
-    <t>demiromantic</t>
-  </si>
-  <si>
-    <t>aro</t>
-  </si>
-  <si>
-    <t>spectrum</t>
-  </si>
-  <si>
-    <t>people</t>
+    <t>sexual</t>
+  </si>
+  <si>
+    <t>really</t>
+  </si>
+  <si>
+    <t>unsure</t>
+  </si>
+  <si>
+    <t>and ace</t>
+  </si>
+  <si>
+    <t>bisexual and</t>
+  </si>
+  <si>
+    <t>relevant to</t>
+  </si>
+  <si>
+    <t>should not</t>
+  </si>
+  <si>
+    <t>not be</t>
+  </si>
+  <si>
+    <t>dont care</t>
+  </si>
+  <si>
+    <t>pan sexual</t>
+  </si>
+  <si>
+    <t>abrosexual</t>
+  </si>
+  <si>
+    <t>mujer</t>
+  </si>
+  <si>
+    <t>attracted</t>
+  </si>
+  <si>
+    <t>cars</t>
+  </si>
+  <si>
+    <t>on</t>
+  </si>
+  <si>
+    <t>heteroflexible</t>
+  </si>
+  <si>
+    <t>like</t>
+  </si>
+  <si>
+    <t>yet</t>
   </si>
   <si>
     <t>demi</t>
   </si>
   <si>
-    <t>labeled</t>
-  </si>
-  <si>
-    <t>bicurious</t>
+    <t>its</t>
+  </si>
+  <si>
+    <t>mine</t>
+  </si>
+  <si>
+    <t>do</t>
+  </si>
+  <si>
+    <t>myself</t>
+  </si>
+  <si>
+    <t>hate</t>
   </si>
   <si>
     <t>heterosexual</t>
   </si>
   <si>
-    <t>minor</t>
-  </si>
-  <si>
-    <t>sexual</t>
-  </si>
-  <si>
-    <t>really</t>
-  </si>
-  <si>
-    <t>care</t>
-  </si>
-  <si>
-    <t>unsure</t>
-  </si>
-  <si>
-    <t>pan sexual</t>
-  </si>
-  <si>
-    <t>abrosexual</t>
-  </si>
-  <si>
-    <t>mujer</t>
-  </si>
-  <si>
-    <t>attracted</t>
-  </si>
-  <si>
-    <t>cars</t>
-  </si>
-  <si>
-    <t>heteroflexible</t>
-  </si>
-  <si>
-    <t>man</t>
-  </si>
-  <si>
-    <t>yet</t>
-  </si>
-  <si>
-    <t>unlabeledomnisexual</t>
-  </si>
-  <si>
-    <t>information</t>
-  </si>
-  <si>
-    <t>spec</t>
-  </si>
-  <si>
-    <t>even</t>
-  </si>
-  <si>
-    <t>mine</t>
-  </si>
-  <si>
-    <t>anyones</t>
-  </si>
-  <si>
-    <t>experience</t>
-  </si>
-  <si>
-    <t>aroacr</t>
-  </si>
-  <si>
-    <t>hate</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>gay</t>
-  </si>
-  <si>
-    <t>big</t>
-  </si>
-  <si>
-    <t>asking</t>
-  </si>
-  <si>
     <t>question</t>
   </si>
   <si>
+    <t>or</t>
+  </si>
+  <si>
+    <t>also</t>
+  </si>
+  <si>
     <t>none</t>
   </si>
   <si>
+    <t>me</t>
+  </si>
+  <si>
     <t>idk</t>
   </si>
   <si>
@@ -193,9 +217,6 @@
     <t>rest</t>
   </si>
   <si>
-    <t>punishment</t>
-  </si>
-  <si>
     <t>asexualqueer</t>
   </si>
   <si>
@@ -208,13 +229,7 @@
     <t>definitely</t>
   </si>
   <si>
-    <t>matter</t>
-  </si>
-  <si>
-    <t>antrosexual</t>
-  </si>
-  <si>
-    <t>one</t>
+    <t>why</t>
   </si>
   <si>
     <t>hetero</t>
@@ -223,6 +238,21 @@
     <t>polysexual</t>
   </si>
   <si>
+    <t>on both</t>
+  </si>
+  <si>
+    <t>drop table</t>
+  </si>
+  <si>
+    <t>table responses</t>
+  </si>
+  <si>
+    <t>just like</t>
+  </si>
+  <si>
+    <t>panromantic man</t>
+  </si>
+  <si>
     <t>havent switched</t>
   </si>
   <si>
@@ -232,25 +262,142 @@
     <t>sides yet</t>
   </si>
   <si>
+    <t>ace unlabeledomnisexual</t>
+  </si>
+  <si>
+    <t>this is</t>
+  </si>
+  <si>
+    <t>is private</t>
+  </si>
+  <si>
+    <t>private information</t>
+  </si>
+  <si>
+    <t>ace spec</t>
+  </si>
+  <si>
+    <t>demi who</t>
+  </si>
+  <si>
+    <t>who even</t>
+  </si>
+  <si>
+    <t>even knows</t>
+  </si>
+  <si>
     <t>nobodys business</t>
   </si>
   <si>
+    <t>at all</t>
+  </si>
+  <si>
+    <t>all relevant</t>
+  </si>
+  <si>
+    <t>anyones college</t>
+  </si>
+  <si>
+    <t>college experience</t>
+  </si>
+  <si>
+    <t>aroacr biromantic</t>
+  </si>
+  <si>
+    <t>some type</t>
+  </si>
+  <si>
+    <t>type of</t>
+  </si>
+  <si>
+    <t>of gay</t>
+  </si>
+  <si>
+    <t>big titty</t>
+  </si>
+  <si>
+    <t>titty jews</t>
+  </si>
+  <si>
+    <t>jews heterosexual</t>
+  </si>
+  <si>
+    <t>am minor</t>
+  </si>
+  <si>
+    <t>minor you</t>
+  </si>
+  <si>
+    <t>you should</t>
+  </si>
+  <si>
+    <t>be asking</t>
+  </si>
+  <si>
     <t>question cant</t>
   </si>
   <si>
     <t>cant tell</t>
   </si>
   <si>
+    <t>tell if</t>
+  </si>
+  <si>
+    <t>care about</t>
+  </si>
+  <si>
     <t>none apply</t>
   </si>
   <si>
     <t>still figuring</t>
   </si>
   <si>
+    <t>figuring out</t>
+  </si>
+  <si>
+    <t>relevant mentally</t>
+  </si>
+  <si>
+    <t>mentally ill</t>
+  </si>
+  <si>
+    <t>ill people</t>
+  </si>
+  <si>
+    <t>people god</t>
+  </si>
+  <si>
+    <t>god will</t>
+  </si>
+  <si>
     <t>will come</t>
   </si>
   <si>
     <t>will receive</t>
+  </si>
+  <si>
+    <t>receive your</t>
+  </si>
+  <si>
+    <t>your punishment</t>
+  </si>
+  <si>
+    <t>fuck does</t>
+  </si>
+  <si>
+    <t>does this</t>
+  </si>
+  <si>
+    <t>this matter</t>
+  </si>
+  <si>
+    <t>unlabeled antrosexual</t>
+  </si>
+  <si>
+    <t>one wow</t>
+  </si>
+  <si>
+    <t>financial aid</t>
   </si>
   <si>
     <t>trans female</t>
@@ -614,7 +761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B129"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -670,7 +817,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -678,7 +825,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -694,7 +841,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -702,7 +849,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -710,7 +857,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -718,7 +865,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -726,7 +873,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -774,7 +921,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -782,7 +929,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -886,7 +1033,7 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -894,7 +1041,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -902,7 +1049,7 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -910,7 +1057,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -918,7 +1065,7 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -926,7 +1073,7 @@
         <v>39</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -934,7 +1081,7 @@
         <v>40</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -942,7 +1089,7 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -950,7 +1097,7 @@
         <v>42</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -958,7 +1105,7 @@
         <v>43</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1254,6 +1401,398 @@
         <v>80</v>
       </c>
       <c r="B80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>81</v>
+      </c>
+      <c r="B81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>82</v>
+      </c>
+      <c r="B82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
+        <v>83</v>
+      </c>
+      <c r="B83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" t="s">
+        <v>84</v>
+      </c>
+      <c r="B84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>85</v>
+      </c>
+      <c r="B85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>86</v>
+      </c>
+      <c r="B86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" t="s">
+        <v>87</v>
+      </c>
+      <c r="B87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" t="s">
+        <v>88</v>
+      </c>
+      <c r="B88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>89</v>
+      </c>
+      <c r="B89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>90</v>
+      </c>
+      <c r="B90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" t="s">
+        <v>91</v>
+      </c>
+      <c r="B91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" t="s">
+        <v>92</v>
+      </c>
+      <c r="B92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" t="s">
+        <v>93</v>
+      </c>
+      <c r="B93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" t="s">
+        <v>94</v>
+      </c>
+      <c r="B94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" t="s">
+        <v>95</v>
+      </c>
+      <c r="B95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" t="s">
+        <v>96</v>
+      </c>
+      <c r="B96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" t="s">
+        <v>97</v>
+      </c>
+      <c r="B97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" t="s">
+        <v>98</v>
+      </c>
+      <c r="B98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" t="s">
+        <v>99</v>
+      </c>
+      <c r="B99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
+        <v>100</v>
+      </c>
+      <c r="B100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
+        <v>101</v>
+      </c>
+      <c r="B101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" t="s">
+        <v>102</v>
+      </c>
+      <c r="B102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" t="s">
+        <v>103</v>
+      </c>
+      <c r="B103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" t="s">
+        <v>104</v>
+      </c>
+      <c r="B104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" t="s">
+        <v>105</v>
+      </c>
+      <c r="B105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" t="s">
+        <v>106</v>
+      </c>
+      <c r="B106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" t="s">
+        <v>107</v>
+      </c>
+      <c r="B107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" t="s">
+        <v>108</v>
+      </c>
+      <c r="B108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" t="s">
+        <v>109</v>
+      </c>
+      <c r="B109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" t="s">
+        <v>110</v>
+      </c>
+      <c r="B110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" t="s">
+        <v>111</v>
+      </c>
+      <c r="B111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" t="s">
+        <v>112</v>
+      </c>
+      <c r="B112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" t="s">
+        <v>113</v>
+      </c>
+      <c r="B113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" t="s">
+        <v>114</v>
+      </c>
+      <c r="B114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" t="s">
+        <v>115</v>
+      </c>
+      <c r="B115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" t="s">
+        <v>116</v>
+      </c>
+      <c r="B116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" t="s">
+        <v>117</v>
+      </c>
+      <c r="B117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" t="s">
+        <v>118</v>
+      </c>
+      <c r="B118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" t="s">
+        <v>119</v>
+      </c>
+      <c r="B119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" t="s">
+        <v>120</v>
+      </c>
+      <c r="B120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" t="s">
+        <v>121</v>
+      </c>
+      <c r="B121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" t="s">
+        <v>122</v>
+      </c>
+      <c r="B122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" t="s">
+        <v>123</v>
+      </c>
+      <c r="B123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" t="s">
+        <v>124</v>
+      </c>
+      <c r="B124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" t="s">
+        <v>125</v>
+      </c>
+      <c r="B125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" t="s">
+        <v>126</v>
+      </c>
+      <c r="B126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" t="s">
+        <v>127</v>
+      </c>
+      <c r="B127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" t="s">
+        <v>128</v>
+      </c>
+      <c r="B128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" t="s">
+        <v>129</v>
+      </c>
+      <c r="B129">
         <v>1</v>
       </c>
     </row>
